--- a/reports/集团总公司_现金流量表_2026-07.xlsx
+++ b/reports/集团总公司_现金流量表_2026-07.xlsx
@@ -1986,10 +1986,10 @@
         </is>
       </c>
       <c r="F4" s="15" t="n">
-        <v>224952000</v>
+        <v>222125890</v>
       </c>
       <c r="G4" s="15" t="n">
-        <v>1364108928</v>
+        <v>1341132098</v>
       </c>
       <c r="I4" s="5" t="n"/>
     </row>
@@ -2015,10 +2015,10 @@
         </is>
       </c>
       <c r="F5" s="15" t="n">
-        <v>0</v>
+        <v>4469063</v>
       </c>
       <c r="G5" s="15" t="n">
-        <v>0</v>
+        <v>27811784</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -2043,10 +2043,10 @@
         </is>
       </c>
       <c r="F6" s="15" t="n">
-        <v>0</v>
+        <v>2254057</v>
       </c>
       <c r="G6" s="15" t="n">
-        <v>0</v>
+        <v>13917304</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -2071,10 +2071,10 @@
         </is>
       </c>
       <c r="F7" s="15" t="n">
-        <v>0</v>
+        <v>1119447</v>
       </c>
       <c r="G7" s="15" t="n">
-        <v>0</v>
+        <v>6953877</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -2099,10 +2099,10 @@
         </is>
       </c>
       <c r="F8" s="15" t="n">
-        <v>0</v>
+        <v>899243</v>
       </c>
       <c r="G8" s="15" t="n">
-        <v>0</v>
+        <v>5565777</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -2127,10 +2127,10 @@
         </is>
       </c>
       <c r="F9" s="15" t="n">
-        <v>0</v>
+        <v>673742</v>
       </c>
       <c r="G9" s="15" t="n">
-        <v>0</v>
+        <v>4173396</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="F10" s="15" t="n">
-        <v>0</v>
+        <v>448192</v>
       </c>
       <c r="G10" s="15" t="n">
-        <v>0</v>
+        <v>2782111</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -2183,10 +2183,10 @@
         </is>
       </c>
       <c r="F11" s="15" t="n">
-        <v>0</v>
+        <v>337868</v>
       </c>
       <c r="G11" s="15" t="n">
-        <v>0</v>
+        <v>2087271</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
@@ -2211,10 +2211,10 @@
         </is>
       </c>
       <c r="F12" s="15" t="n">
-        <v>0</v>
+        <v>223551</v>
       </c>
       <c r="G12" s="15" t="n">
-        <v>0</v>
+        <v>1390723</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
@@ -2239,10 +2239,10 @@
         </is>
       </c>
       <c r="F13" s="15" t="n">
-        <v>0</v>
+        <v>564031</v>
       </c>
       <c r="G13" s="15" t="n">
-        <v>0</v>
+        <v>3479408</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
@@ -2267,10 +2267,10 @@
         </is>
       </c>
       <c r="F14" s="15" t="n">
-        <v>0</v>
+        <v>280681</v>
       </c>
       <c r="G14" s="15" t="n">
-        <v>0</v>
+        <v>1747140</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -2295,10 +2295,10 @@
         </is>
       </c>
       <c r="F15" s="15" t="n">
-        <v>0</v>
+        <v>179270</v>
       </c>
       <c r="G15" s="15" t="n">
-        <v>0</v>
+        <v>1106286</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -2323,10 +2323,10 @@
         </is>
       </c>
       <c r="F16" s="15" t="n">
-        <v>611408</v>
+        <v>598147</v>
       </c>
       <c r="G16" s="15" t="n">
-        <v>3788546</v>
+        <v>3718494</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -2351,10 +2351,10 @@
         </is>
       </c>
       <c r="F17" s="15" t="n">
-        <v>4152960</v>
+        <v>4091919</v>
       </c>
       <c r="G17" s="15" t="n">
-        <v>25733520</v>
+        <v>25302973</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -2451,7 +2451,7 @@
         </is>
       </c>
       <c r="F21" s="20" t="n">
-        <v>229716368</v>
+        <v>238265101</v>
       </c>
       <c r="G21" s="20" t="n"/>
     </row>
@@ -2477,10 +2477,10 @@
         </is>
       </c>
       <c r="F22" s="15" t="n">
-        <v>138432000</v>
+        <v>136697878</v>
       </c>
       <c r="G22" s="15" t="n">
-        <v>857784000</v>
+        <v>843518412</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -2505,10 +2505,10 @@
         </is>
       </c>
       <c r="F23" s="15" t="n">
-        <v>0</v>
+        <v>1489327</v>
       </c>
       <c r="G23" s="15" t="n">
-        <v>0</v>
+        <v>9270677</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -2533,10 +2533,10 @@
         </is>
       </c>
       <c r="F24" s="15" t="n">
-        <v>0</v>
+        <v>1128057</v>
       </c>
       <c r="G24" s="15" t="n">
-        <v>0</v>
+        <v>6959017</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -2561,10 +2561,10 @@
         </is>
       </c>
       <c r="F25" s="15" t="n">
-        <v>0</v>
+        <v>745179</v>
       </c>
       <c r="G25" s="15" t="n">
-        <v>0</v>
+        <v>4635417</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
@@ -2589,10 +2589,10 @@
         </is>
       </c>
       <c r="F26" s="15" t="n">
-        <v>0</v>
+        <v>563104</v>
       </c>
       <c r="G26" s="15" t="n">
-        <v>0</v>
+        <v>3479145</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
@@ -2617,10 +2617,10 @@
         </is>
       </c>
       <c r="F27" s="15" t="n">
-        <v>0</v>
+        <v>373500</v>
       </c>
       <c r="G27" s="15" t="n">
-        <v>0</v>
+        <v>2318133</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -2645,10 +2645,10 @@
         </is>
       </c>
       <c r="F28" s="15" t="n">
-        <v>0</v>
+        <v>282160</v>
       </c>
       <c r="G28" s="15" t="n">
-        <v>0</v>
+        <v>1748070</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -2673,10 +2673,10 @@
         </is>
       </c>
       <c r="F29" s="15" t="n">
-        <v>27917120</v>
+        <v>27426208</v>
       </c>
       <c r="G29" s="15" t="n">
-        <v>172986440</v>
+        <v>169726127</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -2701,10 +2701,10 @@
         </is>
       </c>
       <c r="F30" s="15" t="n">
-        <v>12920320</v>
+        <v>12649550</v>
       </c>
       <c r="G30" s="15" t="n">
-        <v>80059840</v>
+        <v>78587776</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -2729,10 +2729,10 @@
         </is>
       </c>
       <c r="F31" s="15" t="n">
-        <v>5883360</v>
+        <v>5795446</v>
       </c>
       <c r="G31" s="15" t="n">
-        <v>36455820</v>
+        <v>35779634</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -2781,7 +2781,7 @@
         </is>
       </c>
       <c r="F33" s="20" t="n">
-        <v>185152800</v>
+        <v>187150409</v>
       </c>
       <c r="G33" s="20" t="n"/>
     </row>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="F34" s="20" t="n">
-        <v>44563568</v>
+        <v>51114692</v>
       </c>
       <c r="G34" s="20" t="n"/>
     </row>
@@ -2913,10 +2913,10 @@
         </is>
       </c>
       <c r="F38" s="15" t="n">
-        <v>247200</v>
+        <v>243064</v>
       </c>
       <c r="G38" s="15" t="n">
-        <v>1730400</v>
+        <v>1701185</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -2969,10 +2969,10 @@
         </is>
       </c>
       <c r="F40" s="15" t="n">
-        <v>2163000</v>
+        <v>2130854</v>
       </c>
       <c r="G40" s="15" t="n">
-        <v>15141000</v>
+        <v>14873174</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -2997,10 +2997,10 @@
         </is>
       </c>
       <c r="F41" s="15" t="n">
-        <v>1318400</v>
+        <v>1289461</v>
       </c>
       <c r="G41" s="15" t="n">
-        <v>9228800</v>
+        <v>9061201</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -3025,7 +3025,7 @@
         </is>
       </c>
       <c r="F42" s="20" t="n">
-        <v>2410200</v>
+        <v>2373918</v>
       </c>
       <c r="G42" s="20" t="n"/>
     </row>
@@ -3051,10 +3051,10 @@
         </is>
       </c>
       <c r="F43" s="15" t="n">
-        <v>20600000</v>
+        <v>20079658</v>
       </c>
       <c r="G43" s="15" t="n">
-        <v>144200000</v>
+        <v>141199685</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -3079,10 +3079,10 @@
         </is>
       </c>
       <c r="F44" s="15" t="n">
-        <v>2987000</v>
+        <v>2937290</v>
       </c>
       <c r="G44" s="15" t="n">
-        <v>20909000</v>
+        <v>20475428</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -3107,10 +3107,10 @@
         </is>
       </c>
       <c r="F45" s="15" t="n">
-        <v>14626000</v>
+        <v>14282784</v>
       </c>
       <c r="G45" s="15" t="n">
-        <v>102382000</v>
+        <v>100318815</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -3219,10 +3219,10 @@
         </is>
       </c>
       <c r="F49" s="15" t="n">
-        <v>535600</v>
+        <v>527221</v>
       </c>
       <c r="G49" s="15" t="n">
-        <v>3749200</v>
+        <v>3683026</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -3247,7 +3247,7 @@
         </is>
       </c>
       <c r="F50" s="20" t="n">
-        <v>21135600</v>
+        <v>20606879</v>
       </c>
       <c r="G50" s="20" t="n"/>
     </row>
@@ -3273,7 +3273,7 @@
         </is>
       </c>
       <c r="F51" s="20" t="n">
-        <v>-18725400</v>
+        <v>-18232961</v>
       </c>
       <c r="G51" s="20" t="n"/>
     </row>
@@ -3323,10 +3323,10 @@
         </is>
       </c>
       <c r="F53" s="15" t="n">
-        <v>4841000</v>
+        <v>4783271</v>
       </c>
       <c r="G53" s="15" t="n">
-        <v>33887000</v>
+        <v>33333687</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
@@ -3379,10 +3379,10 @@
         </is>
       </c>
       <c r="F55" s="15" t="n">
-        <v>7725000</v>
+        <v>7614735</v>
       </c>
       <c r="G55" s="15" t="n">
-        <v>54075000</v>
+        <v>53141745</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
@@ -3407,10 +3407,10 @@
         </is>
       </c>
       <c r="F56" s="15" t="n">
-        <v>7725000</v>
+        <v>7575742</v>
       </c>
       <c r="G56" s="15" t="n">
-        <v>54075000</v>
+        <v>53125446</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
@@ -3435,10 +3435,10 @@
         </is>
       </c>
       <c r="F57" s="15" t="n">
-        <v>247200</v>
+        <v>243073</v>
       </c>
       <c r="G57" s="15" t="n">
-        <v>1730400</v>
+        <v>1700900</v>
       </c>
     </row>
     <row r="58" ht="18" customHeight="1">
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="F58" s="20" t="n">
-        <v>12813200</v>
+        <v>12641079</v>
       </c>
       <c r="G58" s="20" t="n"/>
     </row>
@@ -3489,10 +3489,10 @@
         </is>
       </c>
       <c r="F59" s="15" t="n">
-        <v>6283000</v>
+        <v>6157844</v>
       </c>
       <c r="G59" s="15" t="n">
-        <v>43981000</v>
+        <v>43211408</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
@@ -3517,10 +3517,10 @@
         </is>
       </c>
       <c r="F60" s="15" t="n">
-        <v>6283000</v>
+        <v>6199450</v>
       </c>
       <c r="G60" s="15" t="n">
-        <v>43981000</v>
+        <v>43242253</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
@@ -3545,10 +3545,10 @@
         </is>
       </c>
       <c r="F61" s="15" t="n">
-        <v>1030000</v>
+        <v>1007216</v>
       </c>
       <c r="G61" s="15" t="n">
-        <v>7210000</v>
+        <v>7080866</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
@@ -3597,10 +3597,10 @@
         </is>
       </c>
       <c r="F63" s="15" t="n">
-        <v>896100</v>
+        <v>876318</v>
       </c>
       <c r="G63" s="15" t="n">
-        <v>6272700</v>
+        <v>6161098</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="F64" s="15" t="n">
-        <v>128750</v>
+        <v>127006</v>
       </c>
       <c r="G64" s="15" t="n">
-        <v>901250</v>
+        <v>885766</v>
       </c>
     </row>
     <row r="65" ht="18" customHeight="1">
@@ -3653,7 +3653,7 @@
         </is>
       </c>
       <c r="F65" s="20" t="n">
-        <v>7441750</v>
+        <v>7292066</v>
       </c>
       <c r="G65" s="20" t="n"/>
     </row>
@@ -3679,7 +3679,7 @@
         </is>
       </c>
       <c r="F66" s="20" t="n">
-        <v>5371450</v>
+        <v>5349013</v>
       </c>
       <c r="G66" s="20" t="n"/>
     </row>
@@ -3729,7 +3729,7 @@
         </is>
       </c>
       <c r="F68" s="20" t="n">
-        <v>31209618</v>
+        <v>38230744</v>
       </c>
       <c r="G68" s="20" t="n"/>
     </row>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="F70" s="26" t="n">
-        <v>31209618</v>
+        <v>38230744</v>
       </c>
       <c r="G70" s="26" t="n"/>
     </row>
